--- a/artfynd/A 30888-2026 artfynd.xlsx
+++ b/artfynd/A 30888-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531513</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531514</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504685</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531618</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531619</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531621</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531622</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504686</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504688</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1975,6 +2040,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606123</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606158</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2177,6 +2252,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606168</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2276,6 +2356,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531580</t>
         </is>
       </c>
     </row>
@@ -2379,6 +2464,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504663</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2476,6 +2566,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504664</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2577,6 +2672,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531538</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,6 +2774,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504689</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2784,6 +2889,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505153</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2890,6 +3000,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531534</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2999,6 +3114,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504666</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3100,6 +3220,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531569</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3201,6 +3326,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531595</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,6 +3432,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531598</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3403,6 +3538,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531600</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504670</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3597,6 +3742,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504671</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3694,6 +3844,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504672</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3791,6 +3946,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504677</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3888,6 +4048,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504678</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3985,6 +4150,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504679</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4087,6 +4257,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504680</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4184,6 +4359,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505055</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4281,6 +4461,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505056</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4383,6 +4568,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505057</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4480,6 +4670,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505058</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4577,6 +4772,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505059</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4679,6 +4879,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505060</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4780,6 +4985,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531610</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4881,6 +5091,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531500</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4978,6 +5193,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504658</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5079,6 +5299,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531544</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5180,6 +5405,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531546</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5281,6 +5511,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531548</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5382,6 +5617,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531551</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5483,6 +5723,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531552</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5584,6 +5829,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531555</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5681,6 +5931,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505052</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5778,6 +6033,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505054</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5883,8 +6143,67 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>